--- a/artfynd/A 27594-2024 artfynd.xlsx
+++ b/artfynd/A 27594-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119542187</v>
+        <v>119541709</v>
       </c>
       <c r="B2" t="n">
-        <v>86453</v>
+        <v>86336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3739</v>
+        <v>3595</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Siljansspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius dalecarlicus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Berge, Berge, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455090</v>
+        <v>455114</v>
       </c>
       <c r="R2" t="n">
-        <v>7036844</v>
+        <v>7036841</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -753,12 +756,18 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I brant terräng på barrmatta. Både äldre gran och tall växer i närheten.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119541709</v>
+        <v>119542187</v>
       </c>
       <c r="B3" t="n">
-        <v>86336</v>
+        <v>86453</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3595</v>
+        <v>3739</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Siljansspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius dalecarlicus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Berge, Berge, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455114</v>
+        <v>455090</v>
       </c>
       <c r="R3" t="n">
-        <v>7036841</v>
+        <v>7036844</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -858,18 +864,12 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I brant terräng på barrmatta. Både äldre gran och tall växer i närheten.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
